--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/corgon.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/corgon.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="quru" sheetId="1" r:id="rId3"/>
+    <sheet name="quru" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -164,24 +164,6 @@
   </si>
   <si>
     <t xml:space="preserve">mokyu3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">呣啾？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(呣啾)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呣啾啾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呣啾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呣，呣啾。</t>
   </si>
 </sst>
 </file>
@@ -202,19 +184,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -227,7 +209,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -253,7 +235,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -262,62 +244,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -331,13 +313,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -513,26 +495,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,24 +552,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -596,15 +578,12 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
@@ -612,17 +591,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="22.35">
+    <row r="15" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -637,7 +616,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="12.8">
+    <row r="16" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -654,7 +633,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="12.8">
+    <row r="17" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -671,7 +650,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="12.8">
+    <row r="18" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -688,7 +667,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="22.35">
+    <row r="19" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -705,7 +684,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="12.8">
+    <row r="20" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -722,7 +701,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="12.8">
+    <row r="21" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -735,7 +714,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="12.8">
+    <row r="22" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -748,7 +727,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="13.8">
+    <row r="23" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -757,7 +736,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -766,11 +745,9 @@
       <c r="K23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="13.8">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -781,7 +758,7 @@
         <v>24</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -790,11 +767,9 @@
       <c r="K24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="13.8">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -805,7 +780,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -814,11 +789,9 @@
       <c r="K25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="13.8">
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -829,7 +802,7 @@
         <v>22</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -838,11 +811,9 @@
       <c r="K26" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="13.8">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -853,7 +824,7 @@
         <v>36</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -862,11 +833,9 @@
       <c r="K27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="13.8">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -877,7 +846,7 @@
         <v>22</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="1">
+      <c r="I28" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -886,11 +855,9 @@
       <c r="K28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="13.8">
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -901,7 +868,7 @@
         <v>23</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="1">
+      <c r="I29" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J29" s="6" t="s">
@@ -910,11 +877,9 @@
       <c r="K29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="13.8">
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -925,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="1">
+      <c r="I30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J30" s="6" t="s">
@@ -934,11 +899,9 @@
       <c r="K30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="13.8">
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -947,7 +910,7 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="1">
+      <c r="I31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -956,11 +919,9 @@
       <c r="K31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="13.8">
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -971,7 +932,7 @@
         <v>36</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="1">
+      <c r="I32" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -980,11 +941,9 @@
       <c r="K32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="13.8">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -995,7 +954,7 @@
         <v>36</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="1">
+      <c r="I33" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -1004,11 +963,9 @@
       <c r="K33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="13.8">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1021,7 +978,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="13.8">
+    <row r="35" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1034,7 +991,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="13.8">
+    <row r="36" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1047,7 +1004,7 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="22.35">
+    <row r="37" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1062,7 +1019,7 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="12.8">
+    <row r="38" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1075,7 +1032,7 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="12.8">
+    <row r="39" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1088,7 +1045,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="12.8">
+    <row r="40" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1103,7 +1060,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="12.8">
+    <row r="41" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1116,7 +1073,7 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="22.35">
+    <row r="43" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
@@ -1131,7 +1088,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="12.8">
+    <row r="44" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1148,7 +1105,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="22.35">
+    <row r="45" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1163,7 +1120,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="12.8">
+    <row r="46" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1180,7 +1137,7 @@
       </c>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="12.8">
+    <row r="47" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1195,7 +1152,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1208,7 +1165,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="22.35">
+    <row r="50" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>46</v>
       </c>
@@ -1223,7 +1180,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="12.8">
+    <row r="51" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1240,7 +1197,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="12.8">
+    <row r="52" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1257,7 +1214,7 @@
       </c>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="13.8">
+    <row r="53" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1270,7 +1227,7 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="22.35">
+    <row r="54" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1285,7 +1242,7 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="12.8">
+    <row r="55" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1298,7 +1255,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="12.8">
+    <row r="56" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1311,7 +1268,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="12.8">
+    <row r="57" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1328,12 +1285,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/corgon.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/corgon.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="quru" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="quru" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -164,6 +164,24 @@
   </si>
   <si>
     <t xml:space="preserve">mokyu3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">呣啾？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(呣啾)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呣啾啾。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呣啾。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呣，呣啾。</t>
   </si>
 </sst>
 </file>
@@ -184,19 +202,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -209,7 +227,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -235,7 +253,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -244,62 +262,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -313,13 +331,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -495,26 +513,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,24 +570,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="12.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -578,12 +596,15 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
@@ -591,17 +612,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="1" customFormat="1" ht="22.35">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -616,7 +637,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="1" customFormat="1" ht="12.8">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -633,7 +654,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="1" customFormat="1" ht="12.8">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -650,7 +671,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="1" customFormat="1" ht="12.8">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -667,7 +688,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="1" customFormat="1" ht="22.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -684,7 +705,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="1" customFormat="1" ht="12.8">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -701,7 +722,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="1" customFormat="1" ht="12.8">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -714,7 +735,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="1" customFormat="1" ht="12.8">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -727,7 +748,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="1" customFormat="1" ht="13.8">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -736,7 +757,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="1" t="n">
+      <c r="I23" s="1">
         <v>2</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -745,9 +766,11 @@
       <c r="K23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="13.8">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -758,7 +781,7 @@
         <v>24</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -767,9 +790,11 @@
       <c r="K24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="13.8">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -780,7 +805,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="1" t="n">
+      <c r="I25" s="1">
         <v>4</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -789,9 +814,11 @@
       <c r="K25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="13.8">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -802,7 +829,7 @@
         <v>22</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="1" t="n">
+      <c r="I26" s="1">
         <v>5</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -811,9 +838,11 @@
       <c r="K26" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="13.8">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -824,7 +853,7 @@
         <v>36</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -833,9 +862,11 @@
       <c r="K27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="13.8">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -846,7 +877,7 @@
         <v>22</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="1" t="n">
+      <c r="I28" s="1">
         <v>7</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -855,9 +886,11 @@
       <c r="K28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="13.8">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -868,7 +901,7 @@
         <v>23</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="1" t="n">
+      <c r="I29" s="1">
         <v>8</v>
       </c>
       <c r="J29" s="6" t="s">
@@ -877,9 +910,11 @@
       <c r="K29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="13.8">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -890,7 +925,7 @@
         <v>24</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="1" t="n">
+      <c r="I30" s="1">
         <v>9</v>
       </c>
       <c r="J30" s="6" t="s">
@@ -899,9 +934,11 @@
       <c r="K30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="13.8">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -910,7 +947,7 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="1" t="n">
+      <c r="I31" s="1">
         <v>10</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -919,9 +956,11 @@
       <c r="K31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="13.8">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -932,7 +971,7 @@
         <v>36</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="1" t="n">
+      <c r="I32" s="1">
         <v>11</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -941,9 +980,11 @@
       <c r="K32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="13.8">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -954,7 +995,7 @@
         <v>36</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="1" t="n">
+      <c r="I33" s="1">
         <v>12</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -963,9 +1004,11 @@
       <c r="K33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="13.8">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -978,7 +1021,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="1" customFormat="1" ht="13.8">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -991,7 +1034,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="1" customFormat="1" ht="13.8">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1004,7 +1047,7 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="1" customFormat="1" ht="22.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1019,7 +1062,7 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="1" customFormat="1" ht="12.8">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1032,7 +1075,7 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="1" customFormat="1" ht="12.8">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1045,7 +1088,7 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="1" customFormat="1" ht="12.8">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1060,7 +1103,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="1" customFormat="1" ht="12.8">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1073,7 +1116,7 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="43" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="1" customFormat="1" ht="22.35">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
@@ -1088,7 +1131,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="1" customFormat="1" ht="12.8">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1105,7 +1148,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="1" customFormat="1" ht="22.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1120,7 +1163,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="1" customFormat="1" ht="12.8">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1137,7 +1180,7 @@
       </c>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="1" customFormat="1" ht="12.8">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1152,7 +1195,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1165,7 +1208,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="50" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="1" customFormat="1" ht="22.35">
       <c r="A50" s="3" t="s">
         <v>46</v>
       </c>
@@ -1180,7 +1223,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="1" customFormat="1" ht="12.8">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1197,7 +1240,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="1" customFormat="1" ht="12.8">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1214,7 +1257,7 @@
       </c>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="1" customFormat="1" ht="13.8">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1227,7 +1270,7 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="1" customFormat="1" ht="22.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1242,7 +1285,7 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="1" customFormat="1" ht="12.8">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1255,7 +1298,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
-    <row r="56" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="1" customFormat="1" ht="12.8">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1268,7 +1311,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
-    <row r="57" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="1" customFormat="1" ht="12.8">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1285,12 +1328,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
